--- a/2022 data/excel_outputs/4_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/4_boothwise_data.xlsx
@@ -14,11 +14,92 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="450">
   <si>
     <t>AC 4 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
+    <t>Unnamed: 27</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -106,7 +187,7 @@
     <t>PRATHMIK VIDHALYA ROOM NO-1 SARKADI KHUMAR</t>
   </si>
   <si>
-    <t>PRATHMIK VIDHALYA ROOM NO-■ SARKADI KHUMAR</t>
+    <t>PRATHMIK VIDHALYA ROOM NO-1</t>
   </si>
   <si>
     <t>PRATHMIK VIDHALYA ROOM NO-1 SHUMLI</t>
@@ -133,7 +214,7 @@
     <t>PRATHMIK VIDHALYA ROOM NO-1 SULTANPUR</t>
   </si>
   <si>
-    <t>PRATHMIK VIDHALYA ROOM NO-■ SULTANPUR</t>
+    <t>PRATHMIK VIDHAYALYA DAXANI BHAG ROOM NO-2, BOUPUR</t>
   </si>
   <si>
     <t>PURV MADHAYMIC VIDHAYAL ROOM NO-1 DATOLI RANGHAD</t>
@@ -154,7 +235,7 @@
     <t>PRATHMIK VIDHALYA ROOM NO-1 HOGKHEDI</t>
   </si>
   <si>
-    <t>PRATHMIK VIDHALYA ROOM NO-■ HOGKHEDI</t>
+    <t>UNALI PRATHMIK VIDHALYA ROOM NO -1</t>
   </si>
   <si>
     <t>PRATHMIK VIDHAYALYA ROOM NO-1 DABKI GUJAR</t>
@@ -172,10 +253,10 @@
     <t>PRATHMIK VIDHAYALYA ROOM NO-2 ,BOUPUR</t>
   </si>
   <si>
-    <t>PRATHMIK VIDHAYALYA NO-■, ROOM-1,BOUPUR</t>
-  </si>
-  <si>
-    <t>PRATHMIK VIDHAYALYA NO-■, ROOM-2,BOUPUR</t>
+    <t>PRATHMIK VIDHALYA ROOM NO -2</t>
+  </si>
+  <si>
+    <t>GORI SANKAR INDERPAL SINGH INTER COLLEGE HASANPUR ROOM NO -2</t>
   </si>
   <si>
     <t>PRATHMIK VIDHALYA ROOM NO-1 ISHMILEPUR</t>
@@ -340,7 +421,7 @@
     <t>MPS INTER COLLEGE VISHAVKARMA NAGAR ROOM NO-2</t>
   </si>
   <si>
-    <t>MPS INTER COLLEGE VISHAVKARMA NAGAR ROOM NO-■</t>
+    <t>PRATHMIK VIDHALYA DAKSHINI BHAG ROOM NO-2 GYANGADH MAJARA DARAKOTTALA</t>
   </si>
   <si>
     <t>PRATHMIK VIDHALYA ROOM NO -1 MANAKMAU</t>
@@ -832,7 +913,7 @@
     <t>PRATHMIK VIDHALAYA ROOM NO- 1 UGRAHU</t>
   </si>
   <si>
-    <t>PRATHMIK VIDHALAYA ROOM NO- ■ UGRAHU</t>
+    <t>PRATHMIK VIDHALAY DAXANI BHAG , ROOM NO-2 SUBHARI MAHRAAV</t>
   </si>
   <si>
     <t>PRATHMIK VIDHALAYA ROOM NO- 3 UGRAHU</t>
@@ -907,7 +988,7 @@
     <t>PRATHMIK VIDHALAYA ROOM NO-1 GANDEVADA</t>
   </si>
   <si>
-    <t>PRATHMIK VIDHALAYA ROOM NO-■ GANDEVADA</t>
+    <t>PRATHMIK VIDHALAYA PASCHAMI BHAG ROOM NO-2 , PUNDEN</t>
   </si>
   <si>
     <t>PRATHMIK VIDHALAYA ROOM NO-3 GANDEVADA</t>
@@ -1289,8 +1370,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1306,7 +1395,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1314,12 +1403,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1618,94 +1725,175 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:28">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="D2" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="E2" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="F2" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="G2" t="s">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="H2" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="I2" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
       <c r="J2" t="s">
-        <v>405</v>
+        <v>432</v>
       </c>
       <c r="K2" t="s">
-        <v>406</v>
+        <v>433</v>
       </c>
       <c r="L2" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="M2" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="N2" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="O2" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="P2" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="Q2" t="s">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="R2" t="s">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="S2" t="s">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="T2" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="U2" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="V2" t="s">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="W2" t="s">
-        <v>418</v>
+        <v>445</v>
       </c>
       <c r="X2" t="s">
-        <v>419</v>
+        <v>446</v>
       </c>
       <c r="Y2" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="Z2" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="AA2" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="AB2" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:28">
@@ -1713,7 +1901,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C3">
         <v>805</v>
@@ -1799,7 +1987,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>710</v>
@@ -1885,7 +2073,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>718</v>
@@ -1971,7 +2159,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>677</v>
@@ -2057,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>1019</v>
@@ -2143,7 +2331,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>1047</v>
@@ -2229,7 +2417,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>940</v>
@@ -2315,7 +2503,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>1133</v>
@@ -2401,7 +2589,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C11">
         <v>973</v>
@@ -2487,7 +2675,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>972</v>
@@ -2573,7 +2761,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C13">
         <v>1094</v>
@@ -2659,7 +2847,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>1137</v>
@@ -2745,7 +2933,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C15">
         <v>996</v>
@@ -2831,7 +3019,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C16">
         <v>1092</v>
@@ -2917,7 +3105,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="C17">
         <v>1155</v>
@@ -3003,7 +3191,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C18">
         <v>1192</v>
@@ -3089,7 +3277,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="C19">
         <v>624</v>
@@ -3175,7 +3363,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="C20">
         <v>632</v>
@@ -3261,7 +3449,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <v>721</v>
@@ -3347,7 +3535,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C22">
         <v>739</v>
@@ -3433,7 +3621,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C23">
         <v>804</v>
@@ -3519,7 +3707,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="C24">
         <v>735</v>
@@ -3605,7 +3793,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C25">
         <v>719</v>
@@ -3691,7 +3879,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C26">
         <v>920</v>
@@ -3777,7 +3965,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C27">
         <v>1004</v>
@@ -3863,7 +4051,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C28">
         <v>998</v>
@@ -3949,7 +4137,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C29">
         <v>914</v>
@@ -4035,7 +4223,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C30">
         <v>761</v>
@@ -4121,7 +4309,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C31">
         <v>1094</v>
@@ -4207,7 +4395,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C32">
         <v>850</v>
@@ -4293,7 +4481,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C33">
         <v>937</v>
@@ -4379,7 +4567,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C34">
         <v>1028</v>
@@ -4465,7 +4653,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="C35">
         <v>1169</v>
@@ -4551,7 +4739,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C36">
         <v>589</v>
@@ -4637,7 +4825,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="C37">
         <v>622</v>
@@ -4723,7 +4911,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C38">
         <v>795</v>
@@ -4809,7 +4997,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C39">
         <v>929</v>
@@ -4895,7 +5083,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C40">
         <v>876</v>
@@ -4981,7 +5169,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C41">
         <v>861</v>
@@ -5067,7 +5255,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C42">
         <v>856</v>
@@ -5153,7 +5341,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C43">
         <v>772</v>
@@ -5239,7 +5427,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C44">
         <v>650</v>
@@ -5325,7 +5513,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C45">
         <v>943</v>
@@ -5411,7 +5599,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C46">
         <v>1206</v>
@@ -5497,7 +5685,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C47">
         <v>762</v>
@@ -5583,7 +5771,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C48">
         <v>982</v>
@@ -5669,7 +5857,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C49">
         <v>1187</v>
@@ -5755,7 +5943,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C50">
         <v>1031</v>
@@ -5841,7 +6029,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C51">
         <v>824</v>
@@ -5927,7 +6115,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="C52">
         <v>784</v>
@@ -6013,7 +6201,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="C53">
         <v>671</v>
@@ -6099,7 +6287,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="C54">
         <v>662</v>
@@ -6185,7 +6373,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C55">
         <v>1030</v>
@@ -6271,7 +6459,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C56">
         <v>587</v>
@@ -6357,7 +6545,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C57">
         <v>1211</v>
@@ -6443,7 +6631,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C58">
         <v>1123</v>
@@ -6529,7 +6717,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="C59">
         <v>715</v>
@@ -6615,7 +6803,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="C60">
         <v>682</v>
@@ -6701,7 +6889,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C61">
         <v>798</v>
@@ -6787,7 +6975,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C62">
         <v>855</v>
@@ -6873,7 +7061,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="C63">
         <v>779</v>
@@ -6959,7 +7147,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C64">
         <v>688</v>
@@ -7045,7 +7233,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="C65">
         <v>460</v>
@@ -7131,7 +7319,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="C66">
         <v>566</v>
@@ -7217,7 +7405,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C67">
         <v>653</v>
@@ -7303,7 +7491,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="C68">
         <v>644</v>
@@ -7389,7 +7577,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="C69">
         <v>1094</v>
@@ -7475,7 +7663,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="C70">
         <v>640</v>
@@ -7561,7 +7749,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C71">
         <v>678</v>
@@ -7647,7 +7835,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C72">
         <v>917</v>
@@ -7733,7 +7921,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C73">
         <v>949</v>
@@ -7819,7 +8007,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="C74">
         <v>1110</v>
@@ -7905,7 +8093,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C75">
         <v>901</v>
@@ -7991,7 +8179,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C76">
         <v>950</v>
@@ -8077,7 +8265,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="C77">
         <v>1250</v>
@@ -8163,7 +8351,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C78">
         <v>966</v>
@@ -8249,7 +8437,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="C79">
         <v>1164</v>
@@ -8335,7 +8523,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="C80">
         <v>775</v>
@@ -8421,7 +8609,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="C81">
         <v>1117</v>
@@ -8507,7 +8695,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="C82">
         <v>1062</v>
@@ -8593,7 +8781,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="C83">
         <v>1017</v>
@@ -8679,7 +8867,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C84">
         <v>1178</v>
@@ -8765,7 +8953,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C85">
         <v>952</v>
@@ -8851,7 +9039,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C86">
         <v>1051</v>
@@ -8937,7 +9125,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C87">
         <v>1052</v>
@@ -9023,7 +9211,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="C88">
         <v>1102</v>
@@ -9109,7 +9297,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="C89">
         <v>1033</v>
@@ -9195,7 +9383,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="C90">
         <v>954</v>
@@ -9281,7 +9469,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C91">
         <v>958</v>
@@ -9367,7 +9555,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="C92">
         <v>931</v>
@@ -9453,7 +9641,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="C93">
         <v>1018</v>
@@ -9539,7 +9727,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="C94">
         <v>822</v>
@@ -9625,7 +9813,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="C95">
         <v>908</v>
@@ -9711,7 +9899,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C96">
         <v>1192</v>
@@ -9797,7 +9985,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C97">
         <v>1183</v>
@@ -9883,7 +10071,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="C98">
         <v>960</v>
@@ -9969,7 +10157,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="C99">
         <v>757</v>
@@ -10055,7 +10243,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="C100">
         <v>1019</v>
@@ -10141,7 +10329,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="C101">
         <v>1200</v>
@@ -10227,7 +10415,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="C102">
         <v>1063</v>
@@ -10313,7 +10501,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="C103">
         <v>1129</v>
@@ -10399,7 +10587,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="C104">
         <v>941</v>
@@ -10485,7 +10673,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="C105">
         <v>1056</v>
@@ -10571,7 +10759,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="C106">
         <v>1068</v>
@@ -10657,7 +10845,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="C107">
         <v>968</v>
@@ -10743,7 +10931,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="C108">
         <v>1019</v>
@@ -10829,7 +11017,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="C109">
         <v>984</v>
@@ -10915,7 +11103,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="C110">
         <v>1195</v>
@@ -11001,7 +11189,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="C111">
         <v>902</v>
@@ -11087,7 +11275,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="C112">
         <v>1144</v>
@@ -11173,7 +11361,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="C113">
         <v>1202</v>
@@ -11259,7 +11447,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="C114">
         <v>1178</v>
@@ -11345,7 +11533,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="C115">
         <v>1196</v>
@@ -11431,7 +11619,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="C116">
         <v>954</v>
@@ -11517,7 +11705,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="C117">
         <v>762</v>
@@ -11603,7 +11791,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="C118">
         <v>1055</v>
@@ -11689,7 +11877,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="C119">
         <v>1054</v>
@@ -11775,7 +11963,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="C120">
         <v>943</v>
@@ -11861,7 +12049,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="C121">
         <v>971</v>
@@ -11947,7 +12135,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="C122">
         <v>740</v>
@@ -12033,7 +12221,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="C123">
         <v>860</v>
@@ -12119,7 +12307,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="C124">
         <v>939</v>
@@ -12205,7 +12393,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="C125">
         <v>836</v>
@@ -12291,7 +12479,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="C126">
         <v>906</v>
@@ -12377,7 +12565,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="C127">
         <v>620</v>
@@ -12463,7 +12651,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="C128">
         <v>638</v>
@@ -12549,7 +12737,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="C129">
         <v>1232</v>
@@ -12635,7 +12823,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="C130">
         <v>565</v>
@@ -12721,7 +12909,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="C131">
         <v>1039</v>
@@ -12807,7 +12995,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="C132">
         <v>1179</v>
@@ -12893,7 +13081,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="C133">
         <v>807</v>
@@ -12979,7 +13167,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="C134">
         <v>789</v>
@@ -13065,7 +13253,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="C135">
         <v>1215</v>
@@ -13151,7 +13339,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="C136">
         <v>715</v>
@@ -13237,7 +13425,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="C137">
         <v>959</v>
@@ -13323,7 +13511,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="C138">
         <v>762</v>
@@ -13409,7 +13597,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="C139">
         <v>911</v>
@@ -13495,7 +13683,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="C140">
         <v>1146</v>
@@ -13581,7 +13769,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="C141">
         <v>1118</v>
@@ -13667,7 +13855,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="C142">
         <v>863</v>
@@ -13753,7 +13941,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C143">
         <v>747</v>
@@ -13839,7 +14027,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="C144">
         <v>784</v>
@@ -13925,7 +14113,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="C145">
         <v>704</v>
@@ -14011,7 +14199,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="C146">
         <v>1204</v>
@@ -14097,7 +14285,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="C147">
         <v>715</v>
@@ -14183,7 +14371,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="C148">
         <v>739</v>
@@ -14269,7 +14457,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="C149">
         <v>1202</v>
@@ -14355,7 +14543,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="C150">
         <v>927</v>
@@ -14441,7 +14629,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="C151">
         <v>916</v>
@@ -14527,7 +14715,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="C152">
         <v>646</v>
@@ -14613,7 +14801,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="C153">
         <v>779</v>
@@ -14699,7 +14887,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="C154">
         <v>1189</v>
@@ -14785,7 +14973,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C155">
         <v>1110</v>
@@ -14871,7 +15059,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C156">
         <v>1187</v>
@@ -14957,7 +15145,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="C157">
         <v>1111</v>
@@ -15043,7 +15231,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="C158">
         <v>1177</v>
@@ -15129,7 +15317,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="C159">
         <v>1075</v>
@@ -15215,7 +15403,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="C160">
         <v>1104</v>
@@ -15301,7 +15489,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="C161">
         <v>708</v>
@@ -15387,7 +15575,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C162">
         <v>1059</v>
@@ -15473,7 +15661,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="C163">
         <v>1248</v>
@@ -15559,7 +15747,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="C164">
         <v>1167</v>
@@ -15645,7 +15833,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="C165">
         <v>1035</v>
@@ -15731,7 +15919,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="C166">
         <v>727</v>
@@ -15817,7 +16005,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="C167">
         <v>1206</v>
@@ -15903,7 +16091,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="C168">
         <v>773</v>
@@ -15989,7 +16177,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="C169">
         <v>917</v>
@@ -16075,7 +16263,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="C170">
         <v>890</v>
@@ -16161,7 +16349,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="C171">
         <v>1038</v>
@@ -16247,7 +16435,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="C172">
         <v>821</v>
@@ -16333,7 +16521,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C173">
         <v>1117</v>
@@ -16419,7 +16607,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="C174">
         <v>1217</v>
@@ -16505,7 +16693,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="C175">
         <v>1104</v>
@@ -16591,7 +16779,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="C176">
         <v>661</v>
@@ -16677,7 +16865,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="C177">
         <v>598</v>
@@ -16763,7 +16951,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="C178">
         <v>927</v>
@@ -16849,7 +17037,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="C179">
         <v>998</v>
@@ -16935,7 +17123,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="C180">
         <v>838</v>
@@ -17021,7 +17209,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="C181">
         <v>1221</v>
@@ -17107,7 +17295,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="C182">
         <v>744</v>
@@ -17193,7 +17381,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="C183">
         <v>950</v>
@@ -17279,7 +17467,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="C184">
         <v>764</v>
@@ -17365,7 +17553,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="C185">
         <v>888</v>
@@ -17451,7 +17639,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C186">
         <v>736</v>
@@ -17537,7 +17725,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="C187">
         <v>838</v>
@@ -17623,7 +17811,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C188">
         <v>866</v>
@@ -17709,7 +17897,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C189">
         <v>1210</v>
@@ -17795,7 +17983,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C190">
         <v>833</v>
@@ -17881,7 +18069,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="C191">
         <v>666</v>
@@ -17967,7 +18155,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="C192">
         <v>1188</v>
@@ -18053,7 +18241,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="C193">
         <v>825</v>
@@ -18139,7 +18327,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="C194">
         <v>730</v>
@@ -18225,7 +18413,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="C195">
         <v>914</v>
@@ -18311,7 +18499,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="C196">
         <v>926</v>
@@ -18397,7 +18585,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="C197">
         <v>374</v>
@@ -18483,7 +18671,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C198">
         <v>1240</v>
@@ -18569,7 +18757,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="C199">
         <v>1194</v>
@@ -18655,7 +18843,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="C200">
         <v>906</v>
@@ -18741,7 +18929,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="C201">
         <v>883</v>
@@ -18827,7 +19015,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="C202">
         <v>907</v>
@@ -18913,7 +19101,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="C203">
         <v>881</v>
@@ -18999,7 +19187,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="C204">
         <v>1053</v>
@@ -19085,7 +19273,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="C205">
         <v>714</v>
@@ -19171,7 +19359,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="C206">
         <v>690</v>
@@ -19257,7 +19445,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="C207">
         <v>712</v>
@@ -19343,7 +19531,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="C208">
         <v>1017</v>
@@ -19429,7 +19617,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="C209">
         <v>1146</v>
@@ -19515,7 +19703,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="C210">
         <v>865</v>
@@ -19601,7 +19789,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="C211">
         <v>563</v>
@@ -19687,7 +19875,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="C212">
         <v>960</v>
@@ -19773,7 +19961,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="C213">
         <v>670</v>
@@ -19859,7 +20047,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C214">
         <v>628</v>
@@ -19945,7 +20133,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="C215">
         <v>392</v>
@@ -20031,7 +20219,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="C216">
         <v>780</v>
@@ -20117,7 +20305,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="C217">
         <v>1138</v>
@@ -20203,7 +20391,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="C218">
         <v>807</v>
@@ -20289,7 +20477,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="C219">
         <v>495</v>
@@ -20375,7 +20563,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="C220">
         <v>1061</v>
@@ -20461,7 +20649,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="C221">
         <v>1011</v>
@@ -20547,7 +20735,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="C222">
         <v>772</v>
@@ -20633,7 +20821,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="C223">
         <v>945</v>
@@ -20719,7 +20907,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="C224">
         <v>913</v>
@@ -20805,7 +20993,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="C225">
         <v>976</v>
@@ -20891,7 +21079,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="C226">
         <v>594</v>
@@ -20977,7 +21165,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="C227">
         <v>858</v>
@@ -21063,7 +21251,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="C228">
         <v>721</v>
@@ -21149,7 +21337,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="C229">
         <v>914</v>
@@ -21235,7 +21423,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="C230">
         <v>776</v>
@@ -21321,7 +21509,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="C231">
         <v>907</v>
@@ -21407,7 +21595,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="C232">
         <v>896</v>
@@ -21493,7 +21681,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="C233">
         <v>726</v>
@@ -21579,7 +21767,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="C234">
         <v>682</v>
@@ -21665,7 +21853,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="C235">
         <v>706</v>
@@ -21751,7 +21939,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="C236">
         <v>1121</v>
@@ -21837,7 +22025,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="C237">
         <v>1087</v>
@@ -21923,7 +22111,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="C238">
         <v>1098</v>
@@ -22009,7 +22197,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="C239">
         <v>920</v>
@@ -22095,7 +22283,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="C240">
         <v>1008</v>
@@ -22181,7 +22369,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="C241">
         <v>1029</v>
@@ -22267,7 +22455,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="C242">
         <v>1161</v>
@@ -22353,7 +22541,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="C243">
         <v>1235</v>
@@ -22439,7 +22627,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="C244">
         <v>1083</v>
@@ -22525,7 +22713,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="C245">
         <v>1202</v>
@@ -22611,7 +22799,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="C246">
         <v>1221</v>
@@ -22697,7 +22885,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="C247">
         <v>1130</v>
@@ -22783,7 +22971,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="C248">
         <v>1124</v>
@@ -22869,7 +23057,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="C249">
         <v>852</v>
@@ -22955,7 +23143,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="C250">
         <v>842</v>
@@ -23041,7 +23229,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="C251">
         <v>840</v>
@@ -23127,7 +23315,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="C252">
         <v>623</v>
@@ -23213,7 +23401,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="C253">
         <v>620</v>
@@ -23299,7 +23487,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="C254">
         <v>1106</v>
@@ -23385,7 +23573,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="C255">
         <v>1165</v>
@@ -23471,7 +23659,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="C256">
         <v>728</v>
@@ -23557,7 +23745,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="C257">
         <v>949</v>
@@ -23643,7 +23831,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="C258">
         <v>1020</v>
@@ -23729,7 +23917,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C259">
         <v>1119</v>
@@ -23815,7 +24003,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="C260">
         <v>1082</v>
@@ -23901,7 +24089,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="C261">
         <v>909</v>
@@ -23987,7 +24175,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="C262">
         <v>790</v>
@@ -24073,7 +24261,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C263">
         <v>1079</v>
@@ -24159,7 +24347,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="C264">
         <v>1032</v>
@@ -24245,7 +24433,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="C265">
         <v>711</v>
@@ -24331,7 +24519,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="C266">
         <v>650</v>
@@ -24417,7 +24605,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="C267">
         <v>1196</v>
@@ -24503,7 +24691,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="C268">
         <v>877</v>
@@ -24589,7 +24777,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="C269">
         <v>913</v>
@@ -24675,7 +24863,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="C270">
         <v>864</v>
@@ -24761,7 +24949,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="C271">
         <v>802</v>
@@ -24847,7 +25035,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="C272">
         <v>1089</v>
@@ -24933,7 +25121,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="C273">
         <v>965</v>
@@ -25019,7 +25207,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="C274">
         <v>996</v>
@@ -25105,7 +25293,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="C275">
         <v>1060</v>
@@ -25191,7 +25379,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="C276">
         <v>1038</v>
@@ -25277,7 +25465,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="C277">
         <v>1149</v>
@@ -25363,7 +25551,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="C278">
         <v>986</v>
@@ -25449,7 +25637,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="C279">
         <v>1176</v>
@@ -25535,7 +25723,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="C280">
         <v>677</v>
@@ -25621,7 +25809,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="C281">
         <v>609</v>
@@ -25707,7 +25895,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="C282">
         <v>1130</v>
@@ -25793,7 +25981,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="C283">
         <v>787</v>
@@ -25879,7 +26067,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="C284">
         <v>756</v>
@@ -25965,7 +26153,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="C285">
         <v>1009</v>
@@ -26051,7 +26239,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="C286">
         <v>673</v>
@@ -26137,7 +26325,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="C287">
         <v>674</v>
@@ -26223,7 +26411,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="C288">
         <v>620</v>
@@ -26309,7 +26497,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="C289">
         <v>1118</v>
@@ -26395,7 +26583,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="C290">
         <v>620</v>
@@ -26481,7 +26669,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="C291">
         <v>609</v>
@@ -26567,7 +26755,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="C292">
         <v>471</v>
@@ -26653,7 +26841,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>292</v>
+        <v>319</v>
       </c>
       <c r="C293">
         <v>947</v>
@@ -26739,7 +26927,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="C294">
         <v>1215</v>
@@ -26825,7 +27013,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="C295">
         <v>743</v>
@@ -26911,7 +27099,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="C296">
         <v>745</v>
@@ -26997,7 +27185,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="C297">
         <v>963</v>
@@ -27083,7 +27271,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="C298">
         <v>1088</v>
@@ -27169,7 +27357,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="C299">
         <v>1017</v>
@@ -27255,7 +27443,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="C300">
         <v>676</v>
@@ -27341,7 +27529,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C301">
         <v>747</v>
@@ -27427,7 +27615,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="C302">
         <v>688</v>
@@ -27513,7 +27701,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="C303">
         <v>674</v>
@@ -27599,7 +27787,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="C304">
         <v>1088</v>
@@ -27685,7 +27873,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="C305">
         <v>835</v>
@@ -27771,7 +27959,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="C306">
         <v>893</v>
@@ -27857,7 +28045,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>306</v>
+        <v>333</v>
       </c>
       <c r="C307">
         <v>704</v>
@@ -27943,7 +28131,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>307</v>
+        <v>334</v>
       </c>
       <c r="C308">
         <v>921</v>
@@ -28029,7 +28217,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="C309">
         <v>624</v>
@@ -28115,7 +28303,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="C310">
         <v>699</v>
@@ -28201,7 +28389,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="C311">
         <v>1066</v>
@@ -28287,7 +28475,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="C312">
         <v>948</v>
@@ -28373,7 +28561,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>312</v>
+        <v>339</v>
       </c>
       <c r="C313">
         <v>758</v>
@@ -28459,7 +28647,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>313</v>
+        <v>340</v>
       </c>
       <c r="C314">
         <v>776</v>
@@ -28545,7 +28733,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="C315">
         <v>754</v>
@@ -28631,7 +28819,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="C316">
         <v>912</v>
@@ -28717,7 +28905,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="C317">
         <v>1209</v>
@@ -28803,7 +28991,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="C318">
         <v>825</v>
@@ -28889,7 +29077,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="C319">
         <v>712</v>
@@ -28975,7 +29163,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="C320">
         <v>695</v>
@@ -29061,7 +29249,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="C321">
         <v>665</v>
@@ -29147,7 +29335,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="C322">
         <v>879</v>
@@ -29233,7 +29421,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="C323">
         <v>923</v>
@@ -29319,7 +29507,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="C324">
         <v>704</v>
@@ -29405,7 +29593,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="C325">
         <v>598</v>
@@ -29491,7 +29679,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="C326">
         <v>983</v>
@@ -29577,7 +29765,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="C327">
         <v>922</v>
@@ -29663,7 +29851,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="C328">
         <v>710</v>
@@ -29749,7 +29937,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="C329">
         <v>690</v>
@@ -29835,7 +30023,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="C330">
         <v>1204</v>
@@ -29921,7 +30109,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="C331">
         <v>824</v>
@@ -30007,7 +30195,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="C332">
         <v>848</v>
@@ -30093,7 +30281,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="C333">
         <v>864</v>
@@ -30179,7 +30367,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="C334">
         <v>710</v>
@@ -30265,7 +30453,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="C335">
         <v>863</v>
@@ -30351,7 +30539,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="C336">
         <v>977</v>
@@ -30437,7 +30625,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="C337">
         <v>616</v>
@@ -30523,7 +30711,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>337</v>
+        <v>364</v>
       </c>
       <c r="C338">
         <v>622</v>
@@ -30609,7 +30797,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="C339">
         <v>1189</v>
@@ -30695,7 +30883,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="C340">
         <v>988</v>
@@ -30781,7 +30969,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>340</v>
+        <v>367</v>
       </c>
       <c r="C341">
         <v>1064</v>
@@ -30867,7 +31055,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>341</v>
+        <v>368</v>
       </c>
       <c r="C342">
         <v>1122</v>
@@ -30953,7 +31141,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="C343">
         <v>1186</v>
@@ -31039,7 +31227,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="C344">
         <v>1146</v>
@@ -31125,7 +31313,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="C345">
         <v>1142</v>
@@ -31211,7 +31399,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>345</v>
+        <v>372</v>
       </c>
       <c r="C346">
         <v>669</v>
@@ -31297,7 +31485,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="C347">
         <v>767</v>
@@ -31383,7 +31571,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>347</v>
+        <v>374</v>
       </c>
       <c r="C348">
         <v>1153</v>
@@ -31469,7 +31657,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="C349">
         <v>785</v>
@@ -31555,7 +31743,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="C350">
         <v>595</v>
@@ -31641,7 +31829,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="C351">
         <v>1196</v>
@@ -31727,7 +31915,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="C352">
         <v>1227</v>
@@ -31813,7 +32001,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="C353">
         <v>882</v>
@@ -31899,7 +32087,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="C354">
         <v>926</v>
@@ -31985,7 +32173,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="C355">
         <v>880</v>
@@ -32071,7 +32259,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="C356">
         <v>1085</v>
@@ -32157,7 +32345,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="C357">
         <v>1138</v>
@@ -32243,7 +32431,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="C358">
         <v>1111</v>
@@ -32329,7 +32517,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="C359">
         <v>672</v>
@@ -32415,7 +32603,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="C360">
         <v>676</v>
@@ -32501,7 +32689,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="C361">
         <v>782</v>
@@ -32587,7 +32775,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="C362">
         <v>737</v>
@@ -32673,7 +32861,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="C363">
         <v>924</v>
@@ -32759,7 +32947,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="C364">
         <v>1163</v>
@@ -32845,7 +33033,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="C365">
         <v>1113</v>
@@ -32931,7 +33119,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="C366">
         <v>1214</v>
@@ -33017,7 +33205,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="C367">
         <v>1045</v>
@@ -33103,7 +33291,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="C368">
         <v>929</v>
@@ -33189,7 +33377,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="C369">
         <v>681</v>
@@ -33275,7 +33463,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="C370">
         <v>716</v>
@@ -33361,7 +33549,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="C371">
         <v>666</v>
@@ -33447,7 +33635,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="C372">
         <v>1185</v>
@@ -33533,7 +33721,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="C373">
         <v>551</v>
@@ -33619,7 +33807,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="C374">
         <v>670</v>
@@ -33705,7 +33893,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="C375">
         <v>631</v>
@@ -33791,7 +33979,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="C376">
         <v>1058</v>
@@ -33877,7 +34065,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="C377">
         <v>650</v>
@@ -33963,7 +34151,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="C378">
         <v>644</v>
@@ -34049,7 +34237,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="C379">
         <v>1223</v>
@@ -34135,7 +34323,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="C380">
         <v>638</v>
@@ -34221,7 +34409,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="C381">
         <v>613</v>
@@ -34307,7 +34495,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="C382">
         <v>837</v>
@@ -34393,7 +34581,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="C383">
         <v>1095</v>
@@ -34479,7 +34667,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>383</v>
+        <v>410</v>
       </c>
       <c r="C384">
         <v>1034</v>
@@ -34565,7 +34753,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="C385">
         <v>757</v>
@@ -34651,7 +34839,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="C386">
         <v>779</v>
@@ -34737,7 +34925,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="C387">
         <v>962</v>
@@ -34823,7 +35011,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="C388">
         <v>1113</v>
@@ -34909,7 +35097,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="C389">
         <v>906</v>
@@ -34995,7 +35183,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="C390">
         <v>571</v>
@@ -35081,7 +35269,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="C391">
         <v>414</v>
@@ -35167,7 +35355,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="C392">
         <v>1027</v>
@@ -35253,7 +35441,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="C393">
         <v>769</v>
@@ -35339,7 +35527,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="C394">
         <v>1023</v>
@@ -35425,7 +35613,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="C395">
         <v>936</v>
@@ -35511,7 +35699,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="C396">
         <v>871</v>
@@ -35597,7 +35785,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="C397">
         <v>856</v>
@@ -35683,7 +35871,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="C398">
         <v>506</v>
